--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED06.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED06.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:52+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>219W</t>
+          <t>142W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -831,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N3"/>
+  <dimension ref="B2:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -917,6 +917,18 @@
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>贷款时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2季</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>160W</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1712,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0036</t>
+          <t>SIM_XA_FIXED-2-0135</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,11 +1726,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>106W</t>
+          <t>93W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1738,7 +1750,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1季</t>
+          <t>4季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1748,14 +1760,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年2季</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-4-0066</t>
+          <t>SIM_XA_FIXED-3-0067</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1783,19 +1795,19 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>第4年</t>
+          <t>第3年</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>5季</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>4季</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2季</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>-</t>
@@ -1803,14 +1815,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-4-0185</t>
+          <t>SIM_XA_FIXED-4-0068</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1824,11 +1836,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48W</t>
+          <t>160W</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1843,12 +1855,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>5季</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>3季</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1858,7 +1870,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第5年3季</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G54"/>
+  <dimension ref="B2:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2196,10 +2208,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E14" t="n">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2208,7 +2220,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2237,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2263,7 @@
         <v>-14</v>
       </c>
       <c r="E16" t="n">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2277,7 +2289,7 @@
         <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2296,14 +2308,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-14</v>
+        <v>-36</v>
       </c>
       <c r="E18" t="n">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2312,7 +2324,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
         </is>
       </c>
     </row>
@@ -2322,14 +2334,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-15</v>
+        <v>-24</v>
       </c>
       <c r="E19" t="n">
-        <v>413</v>
+        <v>378</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2338,7 +2350,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-be5aa94ba0"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-d6ef454416", "line_id": "L-be5aa94ba0", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2348,14 +2360,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E20" t="n">
-        <v>413</v>
+        <v>364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2364,7 +2376,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-be5aa94ba0", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2374,14 +2386,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E21" t="n">
-        <v>413</v>
+        <v>349</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2402,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-be5aa94ba0", "asset_type": "production_line"}</t>
+          <t>maintenance_expense | {"line_id": "L-be5aa94ba0"}</t>
         </is>
       </c>
     </row>
@@ -2400,23 +2412,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-be5aa94ba0", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2426,23 +2438,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-d3f898b274", "line_id": "L-be5aa94ba0", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-be5aa94ba0", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2456,10 +2468,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E24" t="n">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2485,7 +2497,7 @@
         <v>-14</v>
       </c>
       <c r="E25" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2504,14 +2516,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2520,7 +2532,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 60.0, "order_id": "SIM_XA_FIXED-2-0135", "receivable_term_quarters": 4, "revenue_wan": 93.0}</t>
         </is>
       </c>
     </row>
@@ -2530,23 +2542,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="E27" t="n">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-2-0036", "receivable_term_quarters": 1, "revenue_wan": 106.0}</t>
+          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
         </is>
       </c>
     </row>
@@ -2556,23 +2568,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-48</v>
+        <v>-24</v>
       </c>
       <c r="E28" t="n">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-3b1475684f", "line_id": "L-be5aa94ba0", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2582,23 +2594,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-32</v>
+        <v>-14</v>
       </c>
       <c r="E29" t="n">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-88bbe98c4a", "line_id": "L-be5aa94ba0", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2627,7 @@
         <v>-14</v>
       </c>
       <c r="E30" t="n">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2634,23 +2646,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>106</v>
+        <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>309</v>
+        <v>221</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-a0f73cb028"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2660,14 +2672,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E32" t="n">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2676,7 +2688,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-be5aa94ba0"}</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2698,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>280</v>
+        <v>206</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2702,7 +2714,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-be5aa94ba0"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-be5aa94ba0", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>280</v>
+        <v>206</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2728,7 +2740,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-be5aa94ba0", "asset_type": "factory"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-be5aa94ba0", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2738,23 +2750,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>280</v>
+        <v>206</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-be5aa94ba0", "asset_type": "production_line"}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-3-0067", "receivable_term_quarters": 4, "revenue_wan": 35.0}</t>
         </is>
       </c>
     </row>
@@ -2768,10 +2780,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E36" t="n">
-        <v>272</v>
+        <v>194</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2780,7 +2792,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2809,7 @@
         <v>-14</v>
       </c>
       <c r="E37" t="n">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2816,23 +2828,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="E38" t="n">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-4-0185", "receivable_term_quarters": 4, "revenue_wan": 48.0}</t>
+          <t>receivable_collected | {"receivable_id": "AR-c3ab4d508a"}</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2861,7 @@
         <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2875,7 +2887,7 @@
         <v>-14</v>
       </c>
       <c r="E40" t="n">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2894,14 +2906,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E41" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2910,7 +2922,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-4-0066", "receivable_term_quarters": 2, "revenue_wan": 35.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2920,14 +2932,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-14</v>
+        <v>35</v>
       </c>
       <c r="E42" t="n">
-        <v>216</v>
+        <v>266</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2936,7 +2948,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>receivable_collected | {"receivable_id": "AR-a9dbd7f057"}</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2965,7 @@
         <v>-15</v>
       </c>
       <c r="E43" t="n">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2979,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3005,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3024,14 +3036,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-8</v>
+        <v>-24</v>
       </c>
       <c r="E46" t="n">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3040,7 +3052,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -3050,14 +3062,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="E47" t="n">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3066,7 +3078,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-691c1641b9", "line_id": "L-be5aa94ba0", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -3076,14 +3088,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>48</v>
+        <v>-12</v>
       </c>
       <c r="E48" t="n">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3092,7 +3104,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-9504d6dcee"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -3102,14 +3114,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>35</v>
+        <v>-14</v>
       </c>
       <c r="E49" t="n">
-        <v>262</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3118,7 +3130,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-d46b6d4fd6"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3147,7 @@
         <v>-14</v>
       </c>
       <c r="E50" t="n">
-        <v>248</v>
+        <v>171</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3154,14 +3166,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>234</v>
+        <v>171</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3170,7 +3182,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-4-0068", "receivable_term_quarters": 3, "revenue_wan": 160.0}</t>
         </is>
       </c>
     </row>
@@ -3180,23 +3192,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E52" t="n">
-        <v>219</v>
+        <v>157</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-be5aa94ba0"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3206,14 +3218,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E53" t="n">
-        <v>219</v>
+        <v>142</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3222,7 +3234,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-be5aa94ba0", "asset_type": "factory"}</t>
+          <t>maintenance_expense | {"line_id": "L-be5aa94ba0"}</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>219</v>
+        <v>142</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3247,6 +3259,32 @@
         </is>
       </c>
       <c r="G54" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-be5aa94ba0", "asset_type": "factory"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>142</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-be5aa94ba0", "asset_type": "production_line"}</t>
         </is>
@@ -3353,16 +3391,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3578,16 +3616,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H13" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -3643,13 +3681,13 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="G16" t="n">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17">
@@ -3668,13 +3706,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>60</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" t="n">
         <v>80</v>
-      </c>
-      <c r="G17" t="n">
-        <v>60</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3693,13 +3731,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G18" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
@@ -3715,16 +3753,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H19" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -3740,16 +3778,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-79</v>
+        <v>-83</v>
       </c>
       <c r="F20" t="n">
-        <v>-53</v>
+        <v>-50</v>
       </c>
       <c r="G20" t="n">
-        <v>-56</v>
+        <v>-68</v>
       </c>
       <c r="H20" t="n">
-        <v>-65</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -3790,16 +3828,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-94.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-68.2</v>
+        <v>-65.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-71.2</v>
+        <v>-83.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-80.2</v>
+        <v>-4.199999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -3840,16 +3878,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-94.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-68.2</v>
+        <v>-65.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-71.2</v>
+        <v>-83.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-80.2</v>
+        <v>-4.199999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3890,16 +3928,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-94.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-68.2</v>
+        <v>-65.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-71.2</v>
+        <v>-83.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-80.2</v>
+        <v>-4.199999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3989,16 +4027,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>413</v>
+        <v>349</v>
       </c>
       <c r="F30" t="n">
-        <v>280</v>
+        <v>206</v>
       </c>
       <c r="G30" t="n">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="H30" t="n">
-        <v>219</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31">
@@ -4017,13 +4055,13 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G31" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32">
@@ -4039,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -4067,13 +4105,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4114,16 +4152,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F35" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G35" t="n">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="H35" t="n">
-        <v>239</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36">
@@ -4239,16 +4277,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>494.6</v>
+        <v>490.6</v>
       </c>
       <c r="F40" t="n">
-        <v>426.4</v>
+        <v>425.4</v>
       </c>
       <c r="G40" t="n">
-        <v>355.2</v>
+        <v>342.2</v>
       </c>
       <c r="H40" t="n">
-        <v>275</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41">
@@ -4417,13 +4455,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-180.4</v>
+        <v>-184.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-248.6</v>
+        <v>-249.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-319.8</v>
+        <v>-332.8</v>
       </c>
     </row>
     <row r="48">
@@ -4439,16 +4477,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-94.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-68.2</v>
+        <v>-65.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-71.2</v>
+        <v>-83.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-80.2</v>
+        <v>-4.199999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -4464,16 +4502,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>494.6</v>
+        <v>490.6</v>
       </c>
       <c r="F49" t="n">
-        <v>426.4</v>
+        <v>425.4</v>
       </c>
       <c r="G49" t="n">
-        <v>355.2</v>
+        <v>342.2</v>
       </c>
       <c r="H49" t="n">
-        <v>275</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50">
@@ -4489,16 +4527,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>494.6</v>
+        <v>490.6</v>
       </c>
       <c r="F50" t="n">
-        <v>426.4</v>
+        <v>425.4</v>
       </c>
       <c r="G50" t="n">
-        <v>355.2</v>
+        <v>342.2</v>
       </c>
       <c r="H50" t="n">
-        <v>275</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -4569,7 +4607,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4718,7 +4756,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4867,7 +4905,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5016,7 +5054,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5165,7 +5203,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
